--- a/Sajjad data/by_country_and_state/USA/SD.xlsx
+++ b/Sajjad data/by_country_and_state/USA/SD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
   <si>
     <t>Business Name</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t>2026-10-25T19:35:36.307Z</t>
+  </si>
+  <si>
+    <t>Baer II Alvin L DDS</t>
+  </si>
+  <si>
+    <t>(605) 332-5712</t>
+  </si>
+  <si>
+    <t>3321 E 26th St Unit 1, Sioux Falls, SD 57103</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Baer+II+Alvin+L+DDS/data=!4m7!3m6!1s0x878eb43d5ad43c1d:0xca7c47a242801578!8m2!3d43.5291026!4d-96.6841483!16s%2Fg%2F1tzlzg8v!19sChIJHTzUWj20jocReBWAQqJHfMo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:20:56.158Z</t>
   </si>
 </sst>
 </file>
@@ -634,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1102,6 +1120,47 @@
         <v>80</v>
       </c>
     </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
